--- a/data/Data_ zenrows, Brightdata, Firecrawl_.xlsx
+++ b/data/Data_ zenrows, Brightdata, Firecrawl_.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4314" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4350" uniqueCount="35">
   <si>
     <t>platform</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>BrightData</t>
+  </si>
+  <si>
+    <t>ERROR: &lt;class 'requests.exceptions.ReadTimeout'&gt;</t>
   </si>
   <si>
     <t>Firecrawl ( /scrape endpoint)</t>
@@ -386,11 +389,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1165025800"/>
-        <c:axId val="1455026184"/>
+        <c:axId val="1339157632"/>
+        <c:axId val="345950740"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1165025800"/>
+        <c:axId val="1339157632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -446,10 +449,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1455026184"/>
+        <c:crossAx val="345950740"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1455026184"/>
+        <c:axId val="345950740"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.2"/>
@@ -527,7 +530,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1165025800"/>
+        <c:crossAx val="1339157632"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -652,11 +655,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="898500224"/>
-        <c:axId val="169201975"/>
+        <c:axId val="1944704672"/>
+        <c:axId val="234502688"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="898500224"/>
+        <c:axId val="1944704672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -712,10 +715,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="169201975"/>
+        <c:crossAx val="234502688"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="169201975"/>
+        <c:axId val="234502688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.2"/>
@@ -793,7 +796,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="898500224"/>
+        <c:crossAx val="1944704672"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -835,12 +838,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1000125</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5476875" cy="3190875"/>
+    <xdr:ext cx="6067425" cy="3533775"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="1" name="Chart 1" title="Chart"/>
@@ -3446,9 +3449,10 @@
         <n v="100.0"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="status_code" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1">
+    <cacheField name="status_code">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1">
         <n v="200.0"/>
+        <s v="ERROR: &lt;class 'requests.exceptions.ReadTimeout'&gt;"/>
         <n v="502.0"/>
       </sharedItems>
     </cacheField>
@@ -5725,7 +5729,7 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ZenRows" cacheId="1" dataCaption="" compact="0" compactData="0">
-  <location ref="J3:S13" firstHeaderRow="0" firstDataRow="2" firstDataCol="1"/>
+  <location ref="J3:S13" firstHeaderRow="0" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields>
     <pivotField name="platform" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items>
@@ -5857,7 +5861,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="valid" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+    <pivotField name="valid" axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items>
         <item x="0"/>
         <item x="1"/>
@@ -7095,6 +7099,9 @@
     <field x="3"/>
     <field x="-2"/>
   </colFields>
+  <pageFields>
+    <pageField fld="4"/>
+  </pageFields>
   <dataFields>
     <dataField name="COUNTA of platform" fld="0" subtotal="count" baseField="0"/>
     <dataField name="AVERAGE of secs" fld="5" subtotal="average" baseField="0"/>
@@ -7105,7 +7112,7 @@
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="BrightData" cacheId="2" dataCaption="" compact="0" compactData="0">
-  <location ref="J2:S12" firstHeaderRow="0" firstDataRow="2" firstDataCol="1"/>
+  <location ref="J4:V14" firstHeaderRow="0" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields>
     <pivotField name="platform" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items>
@@ -7233,11 +7240,12 @@
     <pivotField name="status_code" axis="axisCol" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
       <items>
         <item x="0"/>
+        <item x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="valid" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+    <pivotField name="valid" axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items>
         <item x="0"/>
         <item x="1"/>
@@ -8436,6 +8444,9 @@
     <field x="3"/>
     <field x="-2"/>
   </colFields>
+  <pageFields>
+    <pageField fld="4"/>
+  </pageFields>
   <dataFields>
     <dataField name="COUNTA of platform" fld="0" subtotal="count" baseField="0"/>
     <dataField name="AVERAGE of secs" fld="5" subtotal="average" baseField="0"/>
@@ -42882,7 +42893,7 @@
       </c>
       <c r="K15" s="5">
         <f>K12/7</f>
-        <v>99.85714286</v>
+        <v>95.28571429</v>
       </c>
     </row>
     <row r="16">
@@ -45007,8 +45018,8 @@
       <c r="C104" s="3">
         <v>3.0</v>
       </c>
-      <c r="D104" s="2">
-        <v>200.0</v>
+      <c r="D104" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E104" s="4" t="b">
         <v>0</v>
@@ -45175,8 +45186,8 @@
       <c r="C111" s="3">
         <v>10.0</v>
       </c>
-      <c r="D111" s="2">
-        <v>200.0</v>
+      <c r="D111" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E111" s="4" t="b">
         <v>0</v>
@@ -45199,8 +45210,8 @@
       <c r="C112" s="3">
         <v>11.0</v>
       </c>
-      <c r="D112" s="2">
-        <v>200.0</v>
+      <c r="D112" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E112" s="4" t="b">
         <v>0</v>
@@ -45295,8 +45306,8 @@
       <c r="C116" s="3">
         <v>15.0</v>
       </c>
-      <c r="D116" s="2">
-        <v>200.0</v>
+      <c r="D116" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E116" s="4" t="b">
         <v>0</v>
@@ -45343,8 +45354,8 @@
       <c r="C118" s="3">
         <v>17.0</v>
       </c>
-      <c r="D118" s="2">
-        <v>200.0</v>
+      <c r="D118" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E118" s="4" t="b">
         <v>0</v>
@@ -45439,8 +45450,8 @@
       <c r="C122" s="3">
         <v>21.0</v>
       </c>
-      <c r="D122" s="2">
-        <v>200.0</v>
+      <c r="D122" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E122" s="4" t="b">
         <v>0</v>
@@ -45463,8 +45474,8 @@
       <c r="C123" s="3">
         <v>22.0</v>
       </c>
-      <c r="D123" s="2">
-        <v>200.0</v>
+      <c r="D123" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E123" s="4" t="b">
         <v>0</v>
@@ -45535,8 +45546,8 @@
       <c r="C126" s="3">
         <v>25.0</v>
       </c>
-      <c r="D126" s="2">
-        <v>200.0</v>
+      <c r="D126" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E126" s="4" t="b">
         <v>0</v>
@@ -45775,8 +45786,8 @@
       <c r="C136" s="3">
         <v>35.0</v>
       </c>
-      <c r="D136" s="2">
-        <v>200.0</v>
+      <c r="D136" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E136" s="4" t="b">
         <v>0</v>
@@ -45799,8 +45810,8 @@
       <c r="C137" s="3">
         <v>36.0</v>
       </c>
-      <c r="D137" s="2">
-        <v>200.0</v>
+      <c r="D137" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E137" s="4" t="b">
         <v>0</v>
@@ -46087,8 +46098,8 @@
       <c r="C149" s="3">
         <v>48.0</v>
       </c>
-      <c r="D149" s="2">
-        <v>200.0</v>
+      <c r="D149" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E149" s="4" t="b">
         <v>0</v>
@@ -46423,8 +46434,8 @@
       <c r="C163" s="3">
         <v>62.0</v>
       </c>
-      <c r="D163" s="2">
-        <v>200.0</v>
+      <c r="D163" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E163" s="4" t="b">
         <v>0</v>
@@ -46495,8 +46506,8 @@
       <c r="C166" s="3">
         <v>65.0</v>
       </c>
-      <c r="D166" s="2">
-        <v>200.0</v>
+      <c r="D166" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E166" s="4" t="b">
         <v>0</v>
@@ -46519,8 +46530,8 @@
       <c r="C167" s="3">
         <v>66.0</v>
       </c>
-      <c r="D167" s="2">
-        <v>200.0</v>
+      <c r="D167" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E167" s="4" t="b">
         <v>0</v>
@@ -46639,8 +46650,8 @@
       <c r="C172" s="3">
         <v>71.0</v>
       </c>
-      <c r="D172" s="2">
-        <v>200.0</v>
+      <c r="D172" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E172" s="4" t="b">
         <v>0</v>
@@ -46663,8 +46674,8 @@
       <c r="C173" s="3">
         <v>72.0</v>
       </c>
-      <c r="D173" s="2">
-        <v>200.0</v>
+      <c r="D173" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E173" s="4" t="b">
         <v>0</v>
@@ -46735,8 +46746,8 @@
       <c r="C176" s="3">
         <v>75.0</v>
       </c>
-      <c r="D176" s="2">
-        <v>200.0</v>
+      <c r="D176" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E176" s="4" t="b">
         <v>0</v>
@@ -46879,8 +46890,8 @@
       <c r="C182" s="3">
         <v>81.0</v>
       </c>
-      <c r="D182" s="2">
-        <v>200.0</v>
+      <c r="D182" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E182" s="4" t="b">
         <v>0</v>
@@ -46927,8 +46938,8 @@
       <c r="C184" s="3">
         <v>83.0</v>
       </c>
-      <c r="D184" s="2">
-        <v>200.0</v>
+      <c r="D184" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E184" s="4" t="b">
         <v>0</v>
@@ -46951,8 +46962,8 @@
       <c r="C185" s="3">
         <v>84.0</v>
       </c>
-      <c r="D185" s="2">
-        <v>200.0</v>
+      <c r="D185" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E185" s="4" t="b">
         <v>0</v>
@@ -46975,8 +46986,8 @@
       <c r="C186" s="3">
         <v>85.0</v>
       </c>
-      <c r="D186" s="2">
-        <v>200.0</v>
+      <c r="D186" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E186" s="4" t="b">
         <v>0</v>
@@ -46999,8 +47010,8 @@
       <c r="C187" s="3">
         <v>86.0</v>
       </c>
-      <c r="D187" s="2">
-        <v>200.0</v>
+      <c r="D187" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E187" s="4" t="b">
         <v>0</v>
@@ -47023,8 +47034,8 @@
       <c r="C188" s="3">
         <v>87.0</v>
       </c>
-      <c r="D188" s="2">
-        <v>200.0</v>
+      <c r="D188" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E188" s="4" t="b">
         <v>0</v>
@@ -47047,8 +47058,8 @@
       <c r="C189" s="3">
         <v>88.0</v>
       </c>
-      <c r="D189" s="2">
-        <v>200.0</v>
+      <c r="D189" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E189" s="4" t="b">
         <v>0</v>
@@ -47071,8 +47082,8 @@
       <c r="C190" s="3">
         <v>89.0</v>
       </c>
-      <c r="D190" s="2">
-        <v>200.0</v>
+      <c r="D190" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E190" s="4" t="b">
         <v>0</v>
@@ -47095,8 +47106,8 @@
       <c r="C191" s="3">
         <v>90.0</v>
       </c>
-      <c r="D191" s="2">
-        <v>200.0</v>
+      <c r="D191" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E191" s="4" t="b">
         <v>0</v>
@@ -47263,8 +47274,8 @@
       <c r="C198" s="3">
         <v>97.0</v>
       </c>
-      <c r="D198" s="2">
-        <v>200.0</v>
+      <c r="D198" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E198" s="4" t="b">
         <v>0</v>
@@ -49351,8 +49362,8 @@
       <c r="C285" s="3">
         <v>84.0</v>
       </c>
-      <c r="D285" s="2">
-        <v>200.0</v>
+      <c r="D285" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E285" s="4" t="b">
         <v>0</v>
@@ -55039,8 +55050,8 @@
       <c r="C522" s="3">
         <v>21.0</v>
       </c>
-      <c r="D522" s="2">
-        <v>200.0</v>
+      <c r="D522" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E522" s="4" t="b">
         <v>0</v>
@@ -55135,8 +55146,8 @@
       <c r="C526" s="3">
         <v>25.0</v>
       </c>
-      <c r="D526" s="2">
-        <v>200.0</v>
+      <c r="D526" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E526" s="4" t="b">
         <v>0</v>
@@ -55303,8 +55314,8 @@
       <c r="C533" s="3">
         <v>32.0</v>
       </c>
-      <c r="D533" s="2">
-        <v>200.0</v>
+      <c r="D533" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E533" s="4" t="b">
         <v>0</v>
@@ -56695,8 +56706,8 @@
       <c r="C591" s="3">
         <v>90.0</v>
       </c>
-      <c r="D591" s="2">
-        <v>200.0</v>
+      <c r="D591" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E591" s="4" t="b">
         <v>0</v>
@@ -59369,10 +59380,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -59472,10 +59483,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="20" t="s">
         <v>33</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -59505,7 +59516,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="22">
-        <v>1.0</v>
+        <v>0.73</v>
       </c>
       <c r="D5" s="22">
         <v>0.99</v>
@@ -59516,7 +59527,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="22">
-        <v>1.0</v>
+        <v>0.99</v>
       </c>
       <c r="D6" s="22">
         <v>1.0</v>
@@ -59549,7 +59560,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="22">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="D9" s="22">
         <v>1.0</v>
